--- a/Sample Templates/Shikshalokam/Prod_Shikshalokam Observation without rubrics.xlsx
+++ b/Sample Templates/Shikshalokam/Prod_Shikshalokam Observation without rubrics.xlsx
@@ -5,13 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="details" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="criteria" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="questions" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="details" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="criteria" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="questions" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -781,11 +781,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -810,7 +811,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -818,7 +819,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -841,7 +842,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -865,14 +866,6 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
@@ -881,13 +874,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1012,7 +998,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1105,39 +1091,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1149,7 +1127,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1165,10 +1143,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1181,27 +1155,23 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1277,192 +1247,19 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
-  <a:themeElements>
-    <a:clrScheme name="Sheets">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4285f4"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ea4335"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="fbbc04"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="34a853"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="ff6d01"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="46bdc6"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="1155cc"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="1155cc"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Sheets">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E41"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="55.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="2.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="59.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="59.13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1981,21 +1778,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="33.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="33.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="33.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="22.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2046,40 +1842,40 @@
       <c r="F2" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="23" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -2103,39 +1899,38 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="41.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="31" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="32" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2151,1271 +1946,1270 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BK12"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="1" style="0" width="6.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="25.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="15.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="25.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="15.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="J1" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="L1" s="35" t="s">
+      <c r="L1" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="M1" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="N1" s="35" t="s">
+      <c r="N1" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="O1" s="35" t="s">
+      <c r="O1" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="P1" s="35" t="s">
+      <c r="P1" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Q1" s="35" t="s">
+      <c r="Q1" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="T1" s="32" t="s">
+      <c r="T1" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="U1" s="32" t="s">
+      <c r="U1" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="V1" s="32" t="s">
+      <c r="V1" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="W1" s="35" t="s">
+      <c r="W1" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="X1" s="36" t="s">
+      <c r="X1" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="36"/>
-      <c r="AK1" s="36"/>
-      <c r="AL1" s="36"/>
-      <c r="AM1" s="36"/>
-      <c r="AN1" s="36"/>
-      <c r="AO1" s="36"/>
-      <c r="AP1" s="36"/>
-      <c r="AQ1" s="36"/>
-      <c r="AR1" s="36"/>
-      <c r="AS1" s="36"/>
-      <c r="AT1" s="36"/>
-      <c r="AU1" s="36"/>
-      <c r="AV1" s="36"/>
-      <c r="AW1" s="36"/>
-      <c r="AX1" s="36"/>
-      <c r="AY1" s="36"/>
-      <c r="AZ1" s="36"/>
-      <c r="BA1" s="36"/>
-      <c r="BB1" s="36"/>
-      <c r="BC1" s="36"/>
-      <c r="BD1" s="36"/>
-      <c r="BE1" s="36"/>
-      <c r="BF1" s="36"/>
-      <c r="BG1" s="36"/>
-      <c r="BH1" s="36"/>
-      <c r="BI1" s="36"/>
-      <c r="BJ1" s="35" t="s">
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="34"/>
+      <c r="AR1" s="34"/>
+      <c r="AS1" s="34"/>
+      <c r="AT1" s="34"/>
+      <c r="AU1" s="34"/>
+      <c r="AV1" s="34"/>
+      <c r="AW1" s="34"/>
+      <c r="AX1" s="34"/>
+      <c r="AY1" s="34"/>
+      <c r="AZ1" s="34"/>
+      <c r="BA1" s="34"/>
+      <c r="BB1" s="34"/>
+      <c r="BC1" s="34"/>
+      <c r="BD1" s="34"/>
+      <c r="BE1" s="34"/>
+      <c r="BF1" s="34"/>
+      <c r="BG1" s="34"/>
+      <c r="BH1" s="34"/>
+      <c r="BI1" s="34"/>
+      <c r="BJ1" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="BK1" s="35" t="s">
+      <c r="BK1" s="30" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="N2" s="39" t="s">
+      <c r="N2" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="O2" s="37" t="s">
+      <c r="O2" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="39" t="s">
+      <c r="P2" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="Q2" s="41" t="s">
+      <c r="Q2" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="R2" s="39" t="s">
+      <c r="R2" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="39" t="s">
+      <c r="S2" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="T2" s="42" t="s">
+      <c r="T2" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="U2" s="40" t="s">
+      <c r="U2" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="V2" s="39" t="s">
+      <c r="V2" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="W2" s="40" t="s">
+      <c r="W2" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="X2" s="39" t="s">
+      <c r="X2" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="40" t="s">
+      <c r="Y2" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="Z2" s="39" t="s">
+      <c r="Z2" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="AA2" s="40" t="s">
+      <c r="AA2" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="AB2" s="39" t="s">
+      <c r="AB2" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="AC2" s="40" t="s">
+      <c r="AC2" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="AD2" s="39" t="s">
+      <c r="AD2" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="AE2" s="40" t="s">
+      <c r="AE2" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="AF2" s="39" t="s">
+      <c r="AF2" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="AG2" s="40" t="s">
+      <c r="AG2" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="AH2" s="39" t="s">
+      <c r="AH2" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="AI2" s="40" t="s">
+      <c r="AI2" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="AJ2" s="39" t="s">
+      <c r="AJ2" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="AK2" s="40" t="s">
+      <c r="AK2" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="AL2" s="39" t="s">
+      <c r="AL2" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="AM2" s="40" t="s">
+      <c r="AM2" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="AN2" s="39" t="s">
+      <c r="AN2" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="AO2" s="40" t="s">
+      <c r="AO2" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="AP2" s="39" t="s">
+      <c r="AP2" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="AQ2" s="40" t="s">
+      <c r="AQ2" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="AR2" s="39" t="s">
+      <c r="AR2" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="AS2" s="40" t="s">
+      <c r="AS2" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="AT2" s="39" t="s">
+      <c r="AT2" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="AU2" s="40" t="s">
+      <c r="AU2" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="AV2" s="39" t="s">
+      <c r="AV2" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="AW2" s="40" t="s">
+      <c r="AW2" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="AX2" s="39" t="s">
+      <c r="AX2" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="AY2" s="40" t="s">
+      <c r="AY2" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="AZ2" s="39" t="s">
+      <c r="AZ2" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="BA2" s="40" t="s">
+      <c r="BA2" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="BB2" s="39" t="s">
+      <c r="BB2" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="BC2" s="40" t="s">
+      <c r="BC2" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="BD2" s="39" t="s">
+      <c r="BD2" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="BE2" s="40" t="s">
+      <c r="BE2" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="BF2" s="39" t="s">
+      <c r="BF2" s="36" t="s">
         <v>172</v>
       </c>
-      <c r="BG2" s="40" t="s">
+      <c r="BG2" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="BH2" s="39" t="s">
+      <c r="BH2" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="BI2" s="40" t="s">
+      <c r="BI2" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="BJ2" s="40" t="s">
+      <c r="BJ2" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="BK2" s="40" t="s">
+      <c r="BK2" s="37" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="44" t="n">
+      <c r="B3" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44" t="s">
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="44" t="n">
+      <c r="I3" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="41" t="s">
         <v>178</v>
       </c>
-      <c r="K3" s="45"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44" t="s">
+      <c r="K3" s="41"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="46" t="b">
+      <c r="P3" s="40"/>
+      <c r="Q3" s="42" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="46" t="b">
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="U3" s="46" t="b">
+      <c r="U3" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="V3" s="44" t="s">
+      <c r="V3" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="W3" s="44"/>
-      <c r="X3" s="44" t="s">
+      <c r="W3" s="40"/>
+      <c r="X3" s="40" t="s">
         <v>181</v>
       </c>
-      <c r="Y3" s="44"/>
-      <c r="Z3" s="44" t="s">
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="AA3" s="44"/>
-      <c r="AB3" s="44" t="s">
+      <c r="AA3" s="40"/>
+      <c r="AB3" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="AC3" s="44"/>
-      <c r="AD3" s="44" t="s">
+      <c r="AC3" s="40"/>
+      <c r="AD3" s="40" t="s">
         <v>184</v>
       </c>
-      <c r="AE3" s="44"/>
-      <c r="AF3" s="44" t="s">
+      <c r="AE3" s="40"/>
+      <c r="AF3" s="40" t="s">
         <v>185</v>
       </c>
-      <c r="AG3" s="44"/>
-      <c r="AH3" s="44" t="s">
+      <c r="AG3" s="40"/>
+      <c r="AH3" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="AI3" s="44"/>
-      <c r="AJ3" s="44" t="s">
+      <c r="AI3" s="40"/>
+      <c r="AJ3" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="AK3" s="44"/>
-      <c r="AL3" s="44" t="s">
+      <c r="AK3" s="40"/>
+      <c r="AL3" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="AM3" s="44"/>
-      <c r="AN3" s="44" t="s">
+      <c r="AM3" s="40"/>
+      <c r="AN3" s="40" t="s">
         <v>189</v>
       </c>
-      <c r="AO3" s="44"/>
-      <c r="AP3" s="44" t="s">
+      <c r="AO3" s="40"/>
+      <c r="AP3" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="AQ3" s="44"/>
-      <c r="AR3" s="44" t="s">
+      <c r="AQ3" s="40"/>
+      <c r="AR3" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="AS3" s="44"/>
-      <c r="AT3" s="44"/>
-      <c r="AU3" s="44"/>
-      <c r="AV3" s="44"/>
-      <c r="AW3" s="44"/>
-      <c r="AX3" s="44"/>
-      <c r="AY3" s="44"/>
-      <c r="AZ3" s="44"/>
-      <c r="BA3" s="44"/>
-      <c r="BB3" s="44"/>
-      <c r="BC3" s="44"/>
-      <c r="BD3" s="44"/>
-      <c r="BE3" s="44"/>
-      <c r="BF3" s="44"/>
-      <c r="BG3" s="44"/>
-      <c r="BH3" s="44"/>
-      <c r="BI3" s="44"/>
-      <c r="BJ3" s="44"/>
-      <c r="BK3" s="44"/>
+      <c r="AS3" s="40"/>
+      <c r="AT3" s="40"/>
+      <c r="AU3" s="40"/>
+      <c r="AV3" s="40"/>
+      <c r="AW3" s="40"/>
+      <c r="AX3" s="40"/>
+      <c r="AY3" s="40"/>
+      <c r="AZ3" s="40"/>
+      <c r="BA3" s="40"/>
+      <c r="BB3" s="40"/>
+      <c r="BC3" s="40"/>
+      <c r="BD3" s="40"/>
+      <c r="BE3" s="40"/>
+      <c r="BF3" s="40"/>
+      <c r="BG3" s="40"/>
+      <c r="BH3" s="40"/>
+      <c r="BI3" s="40"/>
+      <c r="BJ3" s="40"/>
+      <c r="BK3" s="40"/>
     </row>
     <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="44" t="n">
+      <c r="B4" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="44" t="s">
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="I4" s="44" t="n">
+      <c r="I4" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="45" t="s">
+      <c r="J4" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="K4" s="45"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43" t="s">
+      <c r="K4" s="41"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="P4" s="46" t="b">
+      <c r="P4" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="46" t="b">
+      <c r="Q4" s="42" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="46" t="b">
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="U4" s="46" t="b">
+      <c r="U4" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="V4" s="44"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="43"/>
-      <c r="Z4" s="44"/>
-      <c r="AA4" s="43"/>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="43"/>
-      <c r="AD4" s="44"/>
-      <c r="AE4" s="43"/>
-      <c r="AF4" s="44"/>
-      <c r="AG4" s="43"/>
-      <c r="AH4" s="44"/>
-      <c r="AI4" s="43"/>
-      <c r="AJ4" s="44"/>
-      <c r="AK4" s="43"/>
-      <c r="AL4" s="44"/>
-      <c r="AM4" s="43"/>
-      <c r="AN4" s="43"/>
-      <c r="AO4" s="43"/>
-      <c r="AP4" s="43"/>
-      <c r="AQ4" s="43"/>
-      <c r="AR4" s="43"/>
-      <c r="AS4" s="43"/>
-      <c r="AT4" s="43"/>
-      <c r="AU4" s="43"/>
-      <c r="AV4" s="43"/>
-      <c r="AW4" s="43"/>
-      <c r="AX4" s="43"/>
-      <c r="AY4" s="43"/>
-      <c r="AZ4" s="43"/>
-      <c r="BA4" s="43"/>
-      <c r="BB4" s="43"/>
-      <c r="BC4" s="43"/>
-      <c r="BD4" s="43"/>
-      <c r="BE4" s="43"/>
-      <c r="BF4" s="43"/>
-      <c r="BG4" s="43"/>
-      <c r="BH4" s="43"/>
-      <c r="BI4" s="43"/>
-      <c r="BJ4" s="44"/>
-      <c r="BK4" s="43"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="40"/>
+      <c r="Y4" s="40"/>
+      <c r="Z4" s="40"/>
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="40"/>
+      <c r="AH4" s="40"/>
+      <c r="AI4" s="40"/>
+      <c r="AJ4" s="40"/>
+      <c r="AK4" s="40"/>
+      <c r="AL4" s="40"/>
+      <c r="AM4" s="40"/>
+      <c r="AN4" s="40"/>
+      <c r="AO4" s="40"/>
+      <c r="AP4" s="40"/>
+      <c r="AQ4" s="40"/>
+      <c r="AR4" s="40"/>
+      <c r="AS4" s="40"/>
+      <c r="AT4" s="40"/>
+      <c r="AU4" s="40"/>
+      <c r="AV4" s="40"/>
+      <c r="AW4" s="40"/>
+      <c r="AX4" s="40"/>
+      <c r="AY4" s="40"/>
+      <c r="AZ4" s="40"/>
+      <c r="BA4" s="40"/>
+      <c r="BB4" s="40"/>
+      <c r="BC4" s="40"/>
+      <c r="BD4" s="40"/>
+      <c r="BE4" s="40"/>
+      <c r="BF4" s="40"/>
+      <c r="BG4" s="40"/>
+      <c r="BH4" s="40"/>
+      <c r="BI4" s="40"/>
+      <c r="BJ4" s="40"/>
+      <c r="BK4" s="40"/>
     </row>
     <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="44" t="n">
+      <c r="B5" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44" t="s">
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="I5" s="44" t="n">
+      <c r="I5" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="45" t="s">
+      <c r="J5" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="K5" s="45"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43" t="s">
+      <c r="K5" s="41"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="46" t="b">
+      <c r="P5" s="40"/>
+      <c r="Q5" s="42" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="46" t="b">
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="U5" s="46" t="b">
+      <c r="U5" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="V5" s="45" t="s">
+      <c r="V5" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="W5" s="43"/>
-      <c r="X5" s="45" t="s">
+      <c r="W5" s="40"/>
+      <c r="X5" s="41" t="s">
         <v>198</v>
       </c>
-      <c r="Y5" s="43"/>
-      <c r="Z5" s="45"/>
-      <c r="AA5" s="43"/>
-      <c r="AB5" s="45"/>
-      <c r="AC5" s="43"/>
-      <c r="AD5" s="45"/>
-      <c r="AE5" s="43"/>
-      <c r="AF5" s="45"/>
-      <c r="AG5" s="43"/>
-      <c r="AH5" s="44"/>
-      <c r="AI5" s="43"/>
-      <c r="AJ5" s="44"/>
-      <c r="AK5" s="43"/>
-      <c r="AL5" s="44"/>
-      <c r="AM5" s="43"/>
-      <c r="AN5" s="43"/>
-      <c r="AO5" s="43"/>
-      <c r="AP5" s="43"/>
-      <c r="AQ5" s="43"/>
-      <c r="AR5" s="43"/>
-      <c r="AS5" s="43"/>
-      <c r="AT5" s="43"/>
-      <c r="AU5" s="43"/>
-      <c r="AV5" s="43"/>
-      <c r="AW5" s="43"/>
-      <c r="AX5" s="43"/>
-      <c r="AY5" s="43"/>
-      <c r="AZ5" s="43"/>
-      <c r="BA5" s="43"/>
-      <c r="BB5" s="43"/>
-      <c r="BC5" s="43"/>
-      <c r="BD5" s="43"/>
-      <c r="BE5" s="43"/>
-      <c r="BF5" s="43"/>
-      <c r="BG5" s="43"/>
-      <c r="BH5" s="43"/>
-      <c r="BI5" s="43"/>
-      <c r="BJ5" s="44"/>
-      <c r="BK5" s="43"/>
+      <c r="Y5" s="40"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="40"/>
+      <c r="AB5" s="41"/>
+      <c r="AC5" s="40"/>
+      <c r="AD5" s="41"/>
+      <c r="AE5" s="40"/>
+      <c r="AF5" s="41"/>
+      <c r="AG5" s="40"/>
+      <c r="AH5" s="40"/>
+      <c r="AI5" s="40"/>
+      <c r="AJ5" s="40"/>
+      <c r="AK5" s="40"/>
+      <c r="AL5" s="40"/>
+      <c r="AM5" s="40"/>
+      <c r="AN5" s="40"/>
+      <c r="AO5" s="40"/>
+      <c r="AP5" s="40"/>
+      <c r="AQ5" s="40"/>
+      <c r="AR5" s="40"/>
+      <c r="AS5" s="40"/>
+      <c r="AT5" s="40"/>
+      <c r="AU5" s="40"/>
+      <c r="AV5" s="40"/>
+      <c r="AW5" s="40"/>
+      <c r="AX5" s="40"/>
+      <c r="AY5" s="40"/>
+      <c r="AZ5" s="40"/>
+      <c r="BA5" s="40"/>
+      <c r="BB5" s="40"/>
+      <c r="BC5" s="40"/>
+      <c r="BD5" s="40"/>
+      <c r="BE5" s="40"/>
+      <c r="BF5" s="40"/>
+      <c r="BG5" s="40"/>
+      <c r="BH5" s="40"/>
+      <c r="BI5" s="40"/>
+      <c r="BJ5" s="40"/>
+      <c r="BK5" s="40"/>
     </row>
     <row r="6" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="44" t="n">
+      <c r="B6" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44" t="s">
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="I6" s="44" t="n">
+      <c r="I6" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="J6" s="45" t="s">
+      <c r="J6" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="K6" s="45"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43" t="s">
+      <c r="K6" s="41"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="46" t="b">
+      <c r="P6" s="40"/>
+      <c r="Q6" s="42" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="46" t="b">
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="U6" s="46" t="b">
+      <c r="U6" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="V6" s="45" t="s">
+      <c r="V6" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="W6" s="43"/>
-      <c r="X6" s="45" t="s">
+      <c r="W6" s="40"/>
+      <c r="X6" s="41" t="s">
         <v>198</v>
       </c>
-      <c r="Y6" s="43"/>
-      <c r="Z6" s="45" t="s">
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="AA6" s="43"/>
-      <c r="AB6" s="45"/>
-      <c r="AC6" s="43"/>
-      <c r="AD6" s="45"/>
-      <c r="AE6" s="43"/>
-      <c r="AF6" s="45"/>
-      <c r="AG6" s="43"/>
-      <c r="AH6" s="44"/>
-      <c r="AI6" s="43"/>
-      <c r="AJ6" s="44"/>
-      <c r="AK6" s="43"/>
-      <c r="AL6" s="44"/>
-      <c r="AM6" s="43"/>
-      <c r="AN6" s="43"/>
-      <c r="AO6" s="43"/>
-      <c r="AP6" s="43"/>
-      <c r="AQ6" s="43"/>
-      <c r="AR6" s="43"/>
-      <c r="AS6" s="43"/>
-      <c r="AT6" s="43"/>
-      <c r="AU6" s="43"/>
-      <c r="AV6" s="43"/>
-      <c r="AW6" s="43"/>
-      <c r="AX6" s="43"/>
-      <c r="AY6" s="43"/>
-      <c r="AZ6" s="43"/>
-      <c r="BA6" s="43"/>
-      <c r="BB6" s="43"/>
-      <c r="BC6" s="43"/>
-      <c r="BD6" s="43"/>
-      <c r="BE6" s="43"/>
-      <c r="BF6" s="43"/>
-      <c r="BG6" s="43"/>
-      <c r="BH6" s="43"/>
-      <c r="BI6" s="43"/>
-      <c r="BJ6" s="44"/>
-      <c r="BK6" s="43"/>
+      <c r="AA6" s="40"/>
+      <c r="AB6" s="41"/>
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="41"/>
+      <c r="AE6" s="40"/>
+      <c r="AF6" s="41"/>
+      <c r="AG6" s="40"/>
+      <c r="AH6" s="40"/>
+      <c r="AI6" s="40"/>
+      <c r="AJ6" s="40"/>
+      <c r="AK6" s="40"/>
+      <c r="AL6" s="40"/>
+      <c r="AM6" s="40"/>
+      <c r="AN6" s="40"/>
+      <c r="AO6" s="40"/>
+      <c r="AP6" s="40"/>
+      <c r="AQ6" s="40"/>
+      <c r="AR6" s="40"/>
+      <c r="AS6" s="40"/>
+      <c r="AT6" s="40"/>
+      <c r="AU6" s="40"/>
+      <c r="AV6" s="40"/>
+      <c r="AW6" s="40"/>
+      <c r="AX6" s="40"/>
+      <c r="AY6" s="40"/>
+      <c r="AZ6" s="40"/>
+      <c r="BA6" s="40"/>
+      <c r="BB6" s="40"/>
+      <c r="BC6" s="40"/>
+      <c r="BD6" s="40"/>
+      <c r="BE6" s="40"/>
+      <c r="BF6" s="40"/>
+      <c r="BG6" s="40"/>
+      <c r="BH6" s="40"/>
+      <c r="BI6" s="40"/>
+      <c r="BJ6" s="40"/>
+      <c r="BK6" s="40"/>
     </row>
     <row r="7" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="44" t="n">
+      <c r="B7" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="44" t="s">
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="I7" s="44" t="n">
+      <c r="I7" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="J7" s="45" t="s">
+      <c r="J7" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="K7" s="45"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43" t="s">
+      <c r="K7" s="41"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="46" t="b">
+      <c r="P7" s="40"/>
+      <c r="Q7" s="42" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="46" t="b">
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="U7" s="46" t="b">
+      <c r="U7" s="42" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="V7" s="45" t="s">
+      <c r="V7" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="W7" s="43"/>
-      <c r="X7" s="45" t="s">
+      <c r="W7" s="40"/>
+      <c r="X7" s="41" t="s">
         <v>198</v>
       </c>
-      <c r="Y7" s="43"/>
-      <c r="Z7" s="45" t="s">
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="AA7" s="43"/>
-      <c r="AB7" s="45"/>
-      <c r="AC7" s="43"/>
-      <c r="AD7" s="45"/>
-      <c r="AE7" s="43"/>
-      <c r="AF7" s="45"/>
-      <c r="AG7" s="43"/>
-      <c r="AH7" s="44"/>
-      <c r="AI7" s="43"/>
-      <c r="AJ7" s="44"/>
-      <c r="AK7" s="43"/>
-      <c r="AL7" s="44"/>
-      <c r="AM7" s="43"/>
-      <c r="AN7" s="43"/>
-      <c r="AO7" s="43"/>
-      <c r="AP7" s="43"/>
-      <c r="AQ7" s="43"/>
-      <c r="AR7" s="43"/>
-      <c r="AS7" s="43"/>
-      <c r="AT7" s="43"/>
-      <c r="AU7" s="43"/>
-      <c r="AV7" s="43"/>
-      <c r="AW7" s="43"/>
-      <c r="AX7" s="43"/>
-      <c r="AY7" s="43"/>
-      <c r="AZ7" s="43"/>
-      <c r="BA7" s="43"/>
-      <c r="BB7" s="43"/>
-      <c r="BC7" s="43"/>
-      <c r="BD7" s="43"/>
-      <c r="BE7" s="43"/>
-      <c r="BF7" s="43"/>
-      <c r="BG7" s="43"/>
-      <c r="BH7" s="43"/>
-      <c r="BI7" s="43"/>
-      <c r="BJ7" s="44"/>
-      <c r="BK7" s="43"/>
+      <c r="AA7" s="40"/>
+      <c r="AB7" s="41"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="41"/>
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="41"/>
+      <c r="AG7" s="40"/>
+      <c r="AH7" s="40"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="40"/>
+      <c r="AK7" s="40"/>
+      <c r="AL7" s="40"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="40"/>
+      <c r="AO7" s="40"/>
+      <c r="AP7" s="40"/>
+      <c r="AQ7" s="40"/>
+      <c r="AR7" s="40"/>
+      <c r="AS7" s="40"/>
+      <c r="AT7" s="40"/>
+      <c r="AU7" s="40"/>
+      <c r="AV7" s="40"/>
+      <c r="AW7" s="40"/>
+      <c r="AX7" s="40"/>
+      <c r="AY7" s="40"/>
+      <c r="AZ7" s="40"/>
+      <c r="BA7" s="40"/>
+      <c r="BB7" s="40"/>
+      <c r="BC7" s="40"/>
+      <c r="BD7" s="40"/>
+      <c r="BE7" s="40"/>
+      <c r="BF7" s="40"/>
+      <c r="BG7" s="40"/>
+      <c r="BH7" s="40"/>
+      <c r="BI7" s="40"/>
+      <c r="BJ7" s="40"/>
+      <c r="BK7" s="40"/>
     </row>
     <row r="8" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="44" t="n">
+      <c r="B8" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="D8" s="44"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44" t="s">
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="I8" s="44" t="n">
+      <c r="I8" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="45" t="s">
+      <c r="J8" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="K8" s="45"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43" t="s">
+      <c r="K8" s="41"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="46" t="b">
+      <c r="P8" s="40"/>
+      <c r="Q8" s="42" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R8" s="44"/>
-      <c r="S8" s="44"/>
-      <c r="T8" s="46" t="b">
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="42" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="U8" s="46" t="b">
+      <c r="U8" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="V8" s="45" t="s">
+      <c r="V8" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="W8" s="43"/>
-      <c r="X8" s="45" t="s">
+      <c r="W8" s="40"/>
+      <c r="X8" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="Y8" s="43"/>
-      <c r="Z8" s="45" t="s">
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="AA8" s="43"/>
-      <c r="AB8" s="45"/>
-      <c r="AC8" s="43"/>
-      <c r="AD8" s="45"/>
-      <c r="AE8" s="43"/>
-      <c r="AF8" s="45"/>
-      <c r="AG8" s="43"/>
-      <c r="AH8" s="45"/>
-      <c r="AI8" s="43"/>
-      <c r="AJ8" s="45"/>
-      <c r="AK8" s="43"/>
-      <c r="AL8" s="45"/>
-      <c r="AM8" s="43"/>
-      <c r="AN8" s="43"/>
-      <c r="AO8" s="43"/>
-      <c r="AP8" s="43"/>
-      <c r="AQ8" s="43"/>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
-      <c r="AT8" s="43"/>
-      <c r="AU8" s="43"/>
-      <c r="AV8" s="43"/>
-      <c r="AW8" s="43"/>
-      <c r="AX8" s="43"/>
-      <c r="AY8" s="43"/>
-      <c r="AZ8" s="43"/>
-      <c r="BA8" s="43"/>
-      <c r="BB8" s="43"/>
-      <c r="BC8" s="43"/>
-      <c r="BD8" s="43"/>
-      <c r="BE8" s="43"/>
-      <c r="BF8" s="43"/>
-      <c r="BG8" s="43"/>
-      <c r="BH8" s="43"/>
-      <c r="BI8" s="43"/>
-      <c r="BJ8" s="44"/>
-      <c r="BK8" s="43"/>
+      <c r="AA8" s="40"/>
+      <c r="AB8" s="41"/>
+      <c r="AC8" s="40"/>
+      <c r="AD8" s="41"/>
+      <c r="AE8" s="40"/>
+      <c r="AF8" s="41"/>
+      <c r="AG8" s="40"/>
+      <c r="AH8" s="41"/>
+      <c r="AI8" s="40"/>
+      <c r="AJ8" s="41"/>
+      <c r="AK8" s="40"/>
+      <c r="AL8" s="41"/>
+      <c r="AM8" s="40"/>
+      <c r="AN8" s="40"/>
+      <c r="AO8" s="40"/>
+      <c r="AP8" s="40"/>
+      <c r="AQ8" s="40"/>
+      <c r="AR8" s="40"/>
+      <c r="AS8" s="40"/>
+      <c r="AT8" s="40"/>
+      <c r="AU8" s="40"/>
+      <c r="AV8" s="40"/>
+      <c r="AW8" s="40"/>
+      <c r="AX8" s="40"/>
+      <c r="AY8" s="40"/>
+      <c r="AZ8" s="40"/>
+      <c r="BA8" s="40"/>
+      <c r="BB8" s="40"/>
+      <c r="BC8" s="40"/>
+      <c r="BD8" s="40"/>
+      <c r="BE8" s="40"/>
+      <c r="BF8" s="40"/>
+      <c r="BG8" s="40"/>
+      <c r="BH8" s="40"/>
+      <c r="BI8" s="40"/>
+      <c r="BJ8" s="40"/>
+      <c r="BK8" s="40"/>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="B9" s="44" t="n">
+      <c r="B9" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="40" t="s">
         <v>211</v>
       </c>
-      <c r="D9" s="44"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44" t="s">
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="I9" s="44" t="n">
+      <c r="I9" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="J9" s="45" t="s">
+      <c r="J9" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="K9" s="45"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43" t="s">
+      <c r="K9" s="41"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40" t="s">
         <v>213</v>
       </c>
-      <c r="P9" s="44"/>
-      <c r="Q9" s="46" t="b">
+      <c r="P9" s="40"/>
+      <c r="Q9" s="42" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="46" t="b">
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="U9" s="46" t="b">
+      <c r="U9" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="V9" s="45" t="s">
+      <c r="V9" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="W9" s="43"/>
-      <c r="X9" s="45" t="s">
+      <c r="W9" s="40"/>
+      <c r="X9" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="Y9" s="43"/>
-      <c r="Z9" s="45" t="s">
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="AA9" s="43"/>
-      <c r="AB9" s="45"/>
-      <c r="AC9" s="43"/>
-      <c r="AD9" s="45"/>
-      <c r="AE9" s="43"/>
-      <c r="AF9" s="45"/>
-      <c r="AG9" s="43"/>
-      <c r="AH9" s="43"/>
-      <c r="AI9" s="43"/>
-      <c r="AJ9" s="43"/>
-      <c r="AK9" s="43"/>
-      <c r="AL9" s="43"/>
-      <c r="AM9" s="43"/>
-      <c r="AN9" s="43"/>
-      <c r="AO9" s="43"/>
-      <c r="AP9" s="43"/>
-      <c r="AQ9" s="43"/>
-      <c r="AR9" s="43"/>
-      <c r="AS9" s="43"/>
-      <c r="AT9" s="43"/>
-      <c r="AU9" s="43"/>
-      <c r="AV9" s="43"/>
-      <c r="AW9" s="43"/>
-      <c r="AX9" s="43"/>
-      <c r="AY9" s="43"/>
-      <c r="AZ9" s="43"/>
-      <c r="BA9" s="43"/>
-      <c r="BB9" s="43"/>
-      <c r="BC9" s="43"/>
-      <c r="BD9" s="43"/>
-      <c r="BE9" s="43"/>
-      <c r="BF9" s="43"/>
-      <c r="BG9" s="43"/>
-      <c r="BH9" s="43"/>
-      <c r="BI9" s="43"/>
-      <c r="BJ9" s="44"/>
-      <c r="BK9" s="43"/>
+      <c r="AA9" s="40"/>
+      <c r="AB9" s="41"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="41"/>
+      <c r="AE9" s="40"/>
+      <c r="AF9" s="41"/>
+      <c r="AG9" s="40"/>
+      <c r="AH9" s="40"/>
+      <c r="AI9" s="40"/>
+      <c r="AJ9" s="40"/>
+      <c r="AK9" s="40"/>
+      <c r="AL9" s="40"/>
+      <c r="AM9" s="40"/>
+      <c r="AN9" s="40"/>
+      <c r="AO9" s="40"/>
+      <c r="AP9" s="40"/>
+      <c r="AQ9" s="40"/>
+      <c r="AR9" s="40"/>
+      <c r="AS9" s="40"/>
+      <c r="AT9" s="40"/>
+      <c r="AU9" s="40"/>
+      <c r="AV9" s="40"/>
+      <c r="AW9" s="40"/>
+      <c r="AX9" s="40"/>
+      <c r="AY9" s="40"/>
+      <c r="AZ9" s="40"/>
+      <c r="BA9" s="40"/>
+      <c r="BB9" s="40"/>
+      <c r="BC9" s="40"/>
+      <c r="BD9" s="40"/>
+      <c r="BE9" s="40"/>
+      <c r="BF9" s="40"/>
+      <c r="BG9" s="40"/>
+      <c r="BH9" s="40"/>
+      <c r="BI9" s="40"/>
+      <c r="BJ9" s="40"/>
+      <c r="BK9" s="40"/>
     </row>
     <row r="10" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="B10" s="44" t="n">
+      <c r="B10" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="44" t="s">
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="I10" s="44" t="n">
+      <c r="I10" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="45" t="s">
+      <c r="J10" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="K10" s="45"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="43" t="s">
+      <c r="K10" s="41"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="46" t="b">
+      <c r="P10" s="40"/>
+      <c r="Q10" s="42" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R10" s="44"/>
-      <c r="S10" s="44"/>
-      <c r="T10" s="46" t="b">
+      <c r="R10" s="40"/>
+      <c r="S10" s="40"/>
+      <c r="T10" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="U10" s="46" t="b">
+      <c r="U10" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="V10" s="47"/>
-      <c r="W10" s="43"/>
-      <c r="X10" s="47"/>
-      <c r="Y10" s="43"/>
-      <c r="Z10" s="47"/>
-      <c r="AA10" s="43"/>
-      <c r="AB10" s="47"/>
-      <c r="AC10" s="43"/>
-      <c r="AD10" s="43"/>
-      <c r="AE10" s="43"/>
-      <c r="AF10" s="47"/>
-      <c r="AG10" s="43"/>
-      <c r="AH10" s="43"/>
-      <c r="AI10" s="43"/>
-      <c r="AJ10" s="43"/>
-      <c r="AK10" s="43"/>
-      <c r="AL10" s="43"/>
-      <c r="AM10" s="43"/>
-      <c r="AN10" s="43"/>
-      <c r="AO10" s="43"/>
-      <c r="AP10" s="43"/>
-      <c r="AQ10" s="43"/>
-      <c r="AR10" s="43"/>
-      <c r="AS10" s="43"/>
-      <c r="AT10" s="43"/>
-      <c r="AU10" s="43"/>
-      <c r="AV10" s="43"/>
-      <c r="AW10" s="43"/>
-      <c r="AX10" s="43"/>
-      <c r="AY10" s="43"/>
-      <c r="AZ10" s="43"/>
-      <c r="BA10" s="43"/>
-      <c r="BB10" s="43"/>
-      <c r="BC10" s="43"/>
-      <c r="BD10" s="43"/>
-      <c r="BE10" s="43"/>
-      <c r="BF10" s="43"/>
-      <c r="BG10" s="43"/>
-      <c r="BH10" s="43"/>
-      <c r="BI10" s="43"/>
-      <c r="BJ10" s="44"/>
-      <c r="BK10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="40"/>
+      <c r="X10" s="43"/>
+      <c r="Y10" s="40"/>
+      <c r="Z10" s="43"/>
+      <c r="AA10" s="40"/>
+      <c r="AB10" s="43"/>
+      <c r="AC10" s="40"/>
+      <c r="AD10" s="40"/>
+      <c r="AE10" s="40"/>
+      <c r="AF10" s="43"/>
+      <c r="AG10" s="40"/>
+      <c r="AH10" s="40"/>
+      <c r="AI10" s="40"/>
+      <c r="AJ10" s="40"/>
+      <c r="AK10" s="40"/>
+      <c r="AL10" s="40"/>
+      <c r="AM10" s="40"/>
+      <c r="AN10" s="40"/>
+      <c r="AO10" s="40"/>
+      <c r="AP10" s="40"/>
+      <c r="AQ10" s="40"/>
+      <c r="AR10" s="40"/>
+      <c r="AS10" s="40"/>
+      <c r="AT10" s="40"/>
+      <c r="AU10" s="40"/>
+      <c r="AV10" s="40"/>
+      <c r="AW10" s="40"/>
+      <c r="AX10" s="40"/>
+      <c r="AY10" s="40"/>
+      <c r="AZ10" s="40"/>
+      <c r="BA10" s="40"/>
+      <c r="BB10" s="40"/>
+      <c r="BC10" s="40"/>
+      <c r="BD10" s="40"/>
+      <c r="BE10" s="40"/>
+      <c r="BF10" s="40"/>
+      <c r="BG10" s="40"/>
+      <c r="BH10" s="40"/>
+      <c r="BI10" s="40"/>
+      <c r="BJ10" s="40"/>
+      <c r="BK10" s="40"/>
     </row>
     <row r="11" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="B11" s="44" t="n">
+      <c r="B11" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="40" t="s">
         <v>221</v>
       </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="44" t="s">
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="I11" s="44" t="n">
+      <c r="I11" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="J11" s="45" t="s">
+      <c r="J11" s="41" t="s">
         <v>222</v>
       </c>
-      <c r="K11" s="45"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43" t="s">
+      <c r="K11" s="41"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="46" t="b">
+      <c r="P11" s="40"/>
+      <c r="Q11" s="42" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="46" t="b">
+      <c r="R11" s="40"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="U11" s="46" t="b">
+      <c r="U11" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="V11" s="44" t="s">
+      <c r="V11" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="W11" s="43"/>
-      <c r="X11" s="43" t="s">
+      <c r="W11" s="40"/>
+      <c r="X11" s="40" t="s">
         <v>198</v>
       </c>
-      <c r="Y11" s="43"/>
-      <c r="Z11" s="43" t="s">
+      <c r="Y11" s="40"/>
+      <c r="Z11" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="AA11" s="43"/>
-      <c r="AB11" s="43"/>
-      <c r="AC11" s="43"/>
-      <c r="AD11" s="43"/>
-      <c r="AE11" s="43"/>
-      <c r="AF11" s="43"/>
-      <c r="AG11" s="43"/>
-      <c r="AH11" s="43"/>
-      <c r="AI11" s="43"/>
-      <c r="AJ11" s="43"/>
-      <c r="AK11" s="43"/>
-      <c r="AL11" s="43"/>
-      <c r="AM11" s="43"/>
-      <c r="AN11" s="43"/>
-      <c r="AO11" s="43"/>
-      <c r="AP11" s="43"/>
-      <c r="AQ11" s="43"/>
-      <c r="AR11" s="43"/>
-      <c r="AS11" s="43"/>
-      <c r="AT11" s="43"/>
-      <c r="AU11" s="43"/>
-      <c r="AV11" s="43"/>
-      <c r="AW11" s="43"/>
-      <c r="AX11" s="43"/>
-      <c r="AY11" s="43"/>
-      <c r="AZ11" s="43"/>
-      <c r="BA11" s="43"/>
-      <c r="BB11" s="43"/>
-      <c r="BC11" s="43"/>
-      <c r="BD11" s="43"/>
-      <c r="BE11" s="43"/>
-      <c r="BF11" s="43"/>
-      <c r="BG11" s="43"/>
-      <c r="BH11" s="43"/>
-      <c r="BI11" s="43"/>
-      <c r="BJ11" s="44"/>
-      <c r="BK11" s="43"/>
+      <c r="AA11" s="40"/>
+      <c r="AB11" s="40"/>
+      <c r="AC11" s="40"/>
+      <c r="AD11" s="40"/>
+      <c r="AE11" s="40"/>
+      <c r="AF11" s="40"/>
+      <c r="AG11" s="40"/>
+      <c r="AH11" s="40"/>
+      <c r="AI11" s="40"/>
+      <c r="AJ11" s="40"/>
+      <c r="AK11" s="40"/>
+      <c r="AL11" s="40"/>
+      <c r="AM11" s="40"/>
+      <c r="AN11" s="40"/>
+      <c r="AO11" s="40"/>
+      <c r="AP11" s="40"/>
+      <c r="AQ11" s="40"/>
+      <c r="AR11" s="40"/>
+      <c r="AS11" s="40"/>
+      <c r="AT11" s="40"/>
+      <c r="AU11" s="40"/>
+      <c r="AV11" s="40"/>
+      <c r="AW11" s="40"/>
+      <c r="AX11" s="40"/>
+      <c r="AY11" s="40"/>
+      <c r="AZ11" s="40"/>
+      <c r="BA11" s="40"/>
+      <c r="BB11" s="40"/>
+      <c r="BC11" s="40"/>
+      <c r="BD11" s="40"/>
+      <c r="BE11" s="40"/>
+      <c r="BF11" s="40"/>
+      <c r="BG11" s="40"/>
+      <c r="BH11" s="40"/>
+      <c r="BI11" s="40"/>
+      <c r="BJ11" s="40"/>
+      <c r="BK11" s="40"/>
     </row>
     <row r="12" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="44" t="n">
+      <c r="B12" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="40" t="s">
         <v>224</v>
       </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44" t="s">
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="I12" s="44" t="n">
+      <c r="I12" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="J12" s="45" t="s">
+      <c r="J12" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="K12" s="45"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43" t="s">
+      <c r="K12" s="41"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40" t="s">
         <v>226</v>
       </c>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="46" t="b">
+      <c r="P12" s="40"/>
+      <c r="Q12" s="42" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R12" s="43" t="n">
+      <c r="R12" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="S12" s="43" t="n">
+      <c r="S12" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="T12" s="46" t="b">
+      <c r="T12" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="U12" s="46" t="b">
+      <c r="U12" s="42" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="V12" s="44"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="43"/>
-      <c r="Y12" s="43"/>
-      <c r="Z12" s="43"/>
-      <c r="AA12" s="43"/>
-      <c r="AB12" s="43"/>
-      <c r="AC12" s="43"/>
-      <c r="AD12" s="43"/>
-      <c r="AE12" s="43"/>
-      <c r="AF12" s="43"/>
-      <c r="AG12" s="43"/>
-      <c r="AH12" s="43"/>
-      <c r="AI12" s="43"/>
-      <c r="AJ12" s="43"/>
-      <c r="AK12" s="43"/>
-      <c r="AL12" s="43"/>
-      <c r="AM12" s="43"/>
-      <c r="AN12" s="43"/>
-      <c r="AO12" s="43"/>
-      <c r="AP12" s="43"/>
-      <c r="AQ12" s="43"/>
-      <c r="AR12" s="43"/>
-      <c r="AS12" s="43"/>
-      <c r="AT12" s="43"/>
-      <c r="AU12" s="43"/>
-      <c r="AV12" s="43"/>
-      <c r="AW12" s="43"/>
-      <c r="AX12" s="43"/>
-      <c r="AY12" s="43"/>
-      <c r="AZ12" s="43"/>
-      <c r="BA12" s="43"/>
-      <c r="BB12" s="43"/>
-      <c r="BC12" s="43"/>
-      <c r="BD12" s="43"/>
-      <c r="BE12" s="43"/>
-      <c r="BF12" s="43"/>
-      <c r="BG12" s="43"/>
-      <c r="BH12" s="43"/>
-      <c r="BI12" s="43"/>
-      <c r="BJ12" s="44"/>
-      <c r="BK12" s="43"/>
+      <c r="V12" s="40"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="40"/>
+      <c r="Y12" s="40"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="40"/>
+      <c r="AB12" s="40"/>
+      <c r="AC12" s="40"/>
+      <c r="AD12" s="40"/>
+      <c r="AE12" s="40"/>
+      <c r="AF12" s="40"/>
+      <c r="AG12" s="40"/>
+      <c r="AH12" s="40"/>
+      <c r="AI12" s="40"/>
+      <c r="AJ12" s="40"/>
+      <c r="AK12" s="40"/>
+      <c r="AL12" s="40"/>
+      <c r="AM12" s="40"/>
+      <c r="AN12" s="40"/>
+      <c r="AO12" s="40"/>
+      <c r="AP12" s="40"/>
+      <c r="AQ12" s="40"/>
+      <c r="AR12" s="40"/>
+      <c r="AS12" s="40"/>
+      <c r="AT12" s="40"/>
+      <c r="AU12" s="40"/>
+      <c r="AV12" s="40"/>
+      <c r="AW12" s="40"/>
+      <c r="AX12" s="40"/>
+      <c r="AY12" s="40"/>
+      <c r="AZ12" s="40"/>
+      <c r="BA12" s="40"/>
+      <c r="BB12" s="40"/>
+      <c r="BC12" s="40"/>
+      <c r="BD12" s="40"/>
+      <c r="BE12" s="40"/>
+      <c r="BF12" s="40"/>
+      <c r="BG12" s="40"/>
+      <c r="BH12" s="40"/>
+      <c r="BI12" s="40"/>
+      <c r="BJ12" s="40"/>
+      <c r="BK12" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
